--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136817673</v>
       </c>
       <c r="B7" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>136819185</v>
       </c>
       <c r="B8" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136817673</v>
       </c>
       <c r="B7" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>136819185</v>
       </c>
       <c r="B8" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -1348,11 +1348,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mickelstjärn, Mickelstjärn, Dlr</t>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136817673</v>
       </c>
       <c r="B7" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>136819185</v>
       </c>
       <c r="B8" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136817673</v>
       </c>
       <c r="B7" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>136819185</v>
       </c>
       <c r="B8" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38642-2026 artfynd.xlsx
+++ b/artfynd/A 38642-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136820358</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136818828</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136819276</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136818665</v>
       </c>
       <c r="B5" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136819058</v>
       </c>
       <c r="B6" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>136819185</v>
       </c>
       <c r="B8" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136819127</v>
       </c>
       <c r="B9" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136818899</v>
       </c>
       <c r="B10" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
